--- a/uploads/forest_land_excels/CA_-ACA_land.xlsx
+++ b/uploads/forest_land_excels/CA_-ACA_land.xlsx
@@ -5,36 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\forest land data for lims\forest land data for lims\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maasuser\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86854E8A-D9B4-4B69-BB37-744F18EAE589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA3BA92-C659-4DB2-8FF2-8572CFF6CC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="3" r:id="rId1"/>
+    <sheet name="Summary of Column Codes" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="49">
   <si>
     <t>District</t>
   </si>
@@ -42,9 +34,6 @@
     <t>Tahasil</t>
   </si>
   <si>
-    <t>Sl. No.</t>
-  </si>
-  <si>
     <t>RI Circle</t>
   </si>
   <si>
@@ -112,13 +101,85 @@
   </si>
   <si>
     <t>Forest Division</t>
+  </si>
+  <si>
+    <t>CA Land Details</t>
+  </si>
+  <si>
+    <t>Record Details</t>
+  </si>
+  <si>
+    <t>CA Land Area Details</t>
+  </si>
+  <si>
+    <t>column code</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>column name</t>
+  </si>
+  <si>
+    <t>CA02</t>
+  </si>
+  <si>
+    <t>CA03</t>
+  </si>
+  <si>
+    <t>CA04</t>
+  </si>
+  <si>
+    <t>CA05</t>
+  </si>
+  <si>
+    <t>CAD01</t>
+  </si>
+  <si>
+    <t>CAD02</t>
+  </si>
+  <si>
+    <t>CAD03</t>
+  </si>
+  <si>
+    <t>CAD04</t>
+  </si>
+  <si>
+    <t>CAD05</t>
+  </si>
+  <si>
+    <t>CAD06</t>
+  </si>
+  <si>
+    <t>CAD07</t>
+  </si>
+  <si>
+    <t>CAO01</t>
+  </si>
+  <si>
+    <t>CAA01</t>
+  </si>
+  <si>
+    <t>CAA02</t>
+  </si>
+  <si>
+    <t>CAA03</t>
+  </si>
+  <si>
+    <t>CAA04</t>
+  </si>
+  <si>
+    <t>CAA05</t>
+  </si>
+  <si>
+    <t>CAA06</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,16 +187,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -158,16 +239,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,149 +546,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDAB6792-0B21-42AB-8D6E-80AC551EBBEA}">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="19" customWidth="1"/>
-    <col min="12" max="12" width="31.5703125" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1">
-        <v>65</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="K2" s="1">
-        <v>15.843</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="F3" s="1">
         <v>65</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15.843</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1">
+        <v>65</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="1">
+        <v>16</v>
+      </c>
+      <c r="K4" s="1">
+        <v>14.602</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="1">
-        <v>16</v>
-      </c>
-      <c r="K3" s="1">
-        <v>14.602</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="M4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="1" t="s">
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A9FC3F-54E8-4313-8833-1A192F252D9A}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>14</v>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>